--- a/excel_upload_masters/templates/10_finance_core.xlsx
+++ b/excel_upload_masters/templates/10_finance_core.xlsx
@@ -4,12 +4,13 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_monthly_ledger" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_cash_flow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_efficiency_kpis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lists" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_monthly_ledger" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_efficiency_kpis" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,128 +435,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>project_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>reporting_month</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>metric_category</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>budget_value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>forecast_value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>actual_value</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>actual_cost</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>metrics_last_updated_at</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>metrics_last_updated_by_user_id</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>system_created_at</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>system_updated_at</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>source_filename</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>uploaded_by</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Contribution Margin</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Date/datetime — ISO-8601 or Excel date</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Date/datetime — ISO-8601 or Excel date</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Date/datetime — ISO-8601 or Excel date</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Date/datetime — ISO-8601 or Excel date</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Forecast_Joiners</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Revenue_JoiningFee</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Revenue_MMF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Revenue_OpeningFee</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Revenue_PlanningOther</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Revenue_ToBeOfferFee</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -605,6 +549,149 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>metric_category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>budget_value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>forecast_value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>metrics_last_updated_at</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>metrics_last_updated_by_user_id</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>system_created_at</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>system_updated_at</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>source_filename</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>uploaded_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Date/datetime — ISO-8601 or Excel date</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Date/datetime — ISO-8601 or Excel date</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Date/datetime — ISO-8601 or Excel date</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Date/datetime — ISO-8601 or Excel date</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D3:D5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$A$1:$A$9</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>reporting_month</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>unbilled_amount</t>
         </is>
       </c>
@@ -696,7 +783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
